--- a/Result/profitability/6104.xlsx
+++ b/Result/profitability/6104.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.68</v>
       </c>
       <c r="M2" t="n">
-        <v>1.09625</v>
+        <v>1.16375</v>
       </c>
       <c r="N2" t="n">
-        <v>45.07</v>
+        <v>45.3025</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.14</v>
       </c>
       <c r="M3" t="n">
-        <v>0.99</v>
+        <v>0.995</v>
       </c>
       <c r="N3" t="n">
-        <v>43.92625</v>
+        <v>43.5625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.28</v>
       </c>
       <c r="M4" t="n">
-        <v>0.83875</v>
+        <v>0.7337499999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>41.865</v>
+        <v>40.48875</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5512499999999999</v>
+        <v>0.5725</v>
       </c>
       <c r="N5" t="n">
-        <v>39.6725</v>
+        <v>39.3675</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.23</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3525</v>
+        <v>0.42875</v>
       </c>
       <c r="N6" t="n">
-        <v>38.3775</v>
+        <v>38.825</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.08</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2275</v>
+        <v>0.29625</v>
       </c>
       <c r="N7" t="n">
-        <v>37.84375</v>
+        <v>38.255</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.05</v>
       </c>
       <c r="M8" t="n">
-        <v>0.11125</v>
+        <v>0.135</v>
       </c>
       <c r="N8" t="n">
-        <v>37.1825</v>
+        <v>37.30125</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1645,10 +1645,10 @@
         <v>-0.16</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.05875000000000002</v>
+        <v>-0.05875</v>
       </c>
       <c r="N10" t="n">
-        <v>36.86625</v>
+        <v>36.86624999999999</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1772,10 +1772,10 @@
         <v>0.3</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.03875000000000002</v>
+        <v>-0.03874999999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>37.77124999999999</v>
+        <v>37.77125</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -1899,7 +1899,7 @@
         <v>0.26</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.04125000000000002</v>
+        <v>-0.04125</v>
       </c>
       <c r="N12" t="n">
         <v>39.11</v>
@@ -2026,7 +2026,7 @@
         <v>-0.19</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.07375000000000002</v>
+        <v>-0.07375</v>
       </c>
       <c r="N13" t="n">
         <v>38.6075</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6104</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1084</v>
+      </c>
+      <c r="D75" t="n">
+        <v>591</v>
+      </c>
+      <c r="E75" t="n">
+        <v>493</v>
+      </c>
+      <c r="F75" t="n">
+        <v>45.47</v>
+      </c>
+      <c r="G75" t="n">
+        <v>159</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>14.66%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>1</v>
+      </c>
+      <c r="J75" t="n">
+        <v>160</v>
+      </c>
+      <c r="K75" t="n">
+        <v>139</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.3725</v>
+      </c>
+      <c r="N75" t="n">
+        <v>46.305</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.1417910447761193</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.9499999999999957</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.02133872416891269</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-2.439999999999998</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.05092882487998329</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
